--- a/teacher_forms/007_scholarship_recommendation_form--teacher_forms.xlsx
+++ b/teacher_forms/007_scholarship_recommendation_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>School Name</t>
+          <t>School Name2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teachers Name</t>
+          <t>Teacher Name2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Additional Comments2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>School Name</t>
+          <t>School Name3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1352,19 +1352,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>other_scholarships_choices</t>
+          <t>other_recommendations_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,323 +1381,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>other_scholarships_choices</t>
+          <t>other_recommendations_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>other_scholarships_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>other_recommendations_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
